--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1183,17 +1183,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.579</v>
+        <v>4.552</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1185503</v>
+        <v>1178513</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-16052</v>
+        <v>-23042</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-1.92%</t>
         </is>
       </c>
     </row>
@@ -1210,17 +1210,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>54.83</v>
+        <v>54.73</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1162396</v>
+        <v>1160276</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-27348</v>
+        <v>-29468</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-2.48%</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1237,17 @@
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.26</v>
+        <v>32.25</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>848438</v>
+        <v>848175</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-43830</v>
+        <v>-44093</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-4.94%</t>
         </is>
       </c>
     </row>
@@ -1264,17 +1264,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.45</v>
+        <v>28.63</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>264585</v>
+        <v>266259</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5252</v>
+        <v>6926</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+2.67%</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3835102.1</v>
+        <v>3827402.8</v>
       </c>
     </row>
     <row r="5">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4903399.7</v>
+        <v>4895700.4</v>
       </c>
     </row>
     <row r="6">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>-2.09%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1110,6 +1110,416 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>002396</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>358700</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M02</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>深信服</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>300454</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>136.73</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>68365</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M05</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>600664</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>36650</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M04</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>招商轮船</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>601872</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>20760</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M03</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>睿创微纳</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>688002</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>177580</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M01</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>002396</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>135798</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M07</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>恺英网络</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>002517</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>85050</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M09</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>招商轮船</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>601872</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M10</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>225750</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M06</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>新集能源</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>601918</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>98040</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M08</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1121,7 +1531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1641,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>26300</v>
+        <v>19300</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>33.927</v>
@@ -1240,10 +1650,10 @@
         <v>32.25</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>848175</v>
+        <v>622425</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-44093</v>
+        <v>-32357</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1285,7 +1695,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>19000</v>
+        <v>9500</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>10.473</v>
@@ -1294,7 +1704,7 @@
         <v>10.47263157894737</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>198980</v>
+        <v>99490</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -1312,7 +1722,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>17.52</v>
@@ -1321,12 +1731,147 @@
         <v>17.52</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>175200</v>
+        <v>87600</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>星网锐捷</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>6100</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>218807</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>深信服</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>136.73</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>136.73</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>68365</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>哈药股份</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>36650</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>招商轮船</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10380</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>睿创微纳</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>177580</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -1343,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1369,7 +1914,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-18152</v>
+        <v>-29888</v>
       </c>
     </row>
     <row r="3">
@@ -1390,6 +1935,46 @@
       </c>
       <c r="B4" s="2" t="n">
         <v>1884</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>002396</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-4095</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>002517</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>-2550</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>601872</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-380</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>601918</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>-1450</v>
       </c>
     </row>
   </sheetData>
@@ -1439,7 +2024,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1068297.6</v>
+        <v>960880.6</v>
       </c>
     </row>
     <row r="4">
@@ -1449,7 +2034,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3827402.8</v>
+        <v>3926344.8</v>
       </c>
     </row>
     <row r="5">
@@ -1459,7 +2044,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4895700.4</v>
+        <v>4887225.4</v>
       </c>
     </row>
     <row r="6">
@@ -1470,7 +2055,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-2.09%</t>
+          <t>-2.26%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +2066,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2563.56</v>
+        <v>3145.05</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>34.82</v>
+        <v>34.9</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>3900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>135798</v>
+        <v>136110</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>17.01</v>
+        <v>17.1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>5000</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>85050</v>
+        <v>85500</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>20</v>
+        <v>20.16</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>500</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>10000</v>
+        <v>10080</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>32.25</v>
+        <v>32.04</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>7000</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>225750</v>
+        <v>224280</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1515,6 +1515,47 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>603259</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>157700</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M11</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -1531,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1593,17 +1634,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.552</v>
+        <v>4.547</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1178513</v>
+        <v>1177218</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-23042</v>
+        <v>-24337</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>-2.03%</t>
         </is>
       </c>
     </row>
@@ -1620,17 +1661,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>54.73</v>
+        <v>54.13</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1160276</v>
+        <v>1147556</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-29468</v>
+        <v>-42188</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-3.55%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1688,17 @@
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.25</v>
+        <v>32.04</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>622425</v>
+        <v>618372</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-32357</v>
+        <v>-36410</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-4.94%</t>
+          <t>-5.56%</t>
         </is>
       </c>
     </row>
@@ -1674,17 +1715,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.63</v>
+        <v>28.5</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>266259</v>
+        <v>265050</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6926</v>
+        <v>5717</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>+2.20%</t>
         </is>
       </c>
     </row>
@@ -1872,6 +1913,33 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>157700</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -1914,7 +1982,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-29888</v>
+        <v>-31358</v>
       </c>
     </row>
     <row r="3">
@@ -1944,7 +2012,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-4095</v>
+        <v>-3783</v>
       </c>
     </row>
     <row r="6">
@@ -1954,7 +2022,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-2550</v>
+        <v>-2100</v>
       </c>
     </row>
     <row r="7">
@@ -1964,7 +2032,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-380</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="8">
@@ -2024,7 +2092,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>960880.6</v>
+        <v>802552.6</v>
       </c>
     </row>
     <row r="4">
@@ -2034,7 +2102,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3926344.8</v>
+        <v>4064768.3</v>
       </c>
     </row>
     <row r="5">
@@ -2044,7 +2112,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4887225.4</v>
+        <v>4867320.9</v>
       </c>
     </row>
     <row r="6">
@@ -2055,7 +2123,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>-2.65%</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2134,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3145.05</v>
+        <v>3184.01</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1634,17 +1634,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.547</v>
+        <v>4.523</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1177218</v>
+        <v>1171005</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-24337</v>
+        <v>-30550</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>-2.54%</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>54.13</v>
+        <v>53.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1147556</v>
+        <v>1142680</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-42188</v>
+        <v>-47064</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-3.96%</t>
         </is>
       </c>
     </row>
@@ -1688,17 +1688,17 @@
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.04</v>
+        <v>31.68</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>618372</v>
+        <v>611424</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-36410</v>
+        <v>-43358</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>-6.62%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4064768.3</v>
+        <v>4046730.7</v>
       </c>
     </row>
     <row r="5">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4867320.9</v>
+        <v>4849283.3</v>
       </c>
     </row>
     <row r="6">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-3.01%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1634,17 +1634,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.523</v>
+        <v>4.55</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1171005</v>
+        <v>1177995</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-30550</v>
+        <v>-23560</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-1.96%</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.9</v>
+        <v>53.51</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1142680</v>
+        <v>1134412</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-47064</v>
+        <v>-55332</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-4.65%</t>
         </is>
       </c>
     </row>
@@ -1688,17 +1688,17 @@
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31.68</v>
+        <v>32.17</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>611424</v>
+        <v>620881</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-43358</v>
+        <v>-33901</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-6.62%</t>
+          <t>-5.18%</t>
         </is>
       </c>
     </row>
@@ -1715,17 +1715,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.5</v>
+        <v>28.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>265050</v>
+        <v>264678</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5717</v>
+        <v>5345</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+2.20%</t>
+          <t>+2.06%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4046730.7</v>
+        <v>4054538</v>
       </c>
     </row>
     <row r="5">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4849283.3</v>
+        <v>4857090.6</v>
       </c>
     </row>
     <row r="6">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-2.86%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1634,17 +1634,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.55</v>
+        <v>4.523</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1177995</v>
+        <v>1171005</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-23560</v>
+        <v>-30550</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-2.54%</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.51</v>
+        <v>53.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1134412</v>
+        <v>1142680</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-55332</v>
+        <v>-47064</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-4.65%</t>
+          <t>-3.96%</t>
         </is>
       </c>
     </row>
@@ -1688,17 +1688,17 @@
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.17</v>
+        <v>31.68</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>620881</v>
+        <v>611424</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-33901</v>
+        <v>-43358</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-5.18%</t>
+          <t>-6.62%</t>
         </is>
       </c>
     </row>
@@ -1715,17 +1715,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.46</v>
+        <v>28.5</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>264678</v>
+        <v>265050</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5345</v>
+        <v>5717</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+2.06%</t>
+          <t>+2.20%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4054538</v>
+        <v>4046730.7</v>
       </c>
     </row>
     <row r="5">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4857090.6</v>
+        <v>4849283.3</v>
       </c>
     </row>
     <row r="6">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-2.86%</t>
+          <t>-3.01%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>601918</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1460,17 +1460,17 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>32.04</v>
+        <v>10.32</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>7000</v>
+        <v>9500</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>224280</v>
+        <v>98040</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>D20260914M06</t>
+          <t>D20260914M08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1487,31 +1487,31 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>601918</t>
+          <t>603259</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>10.32</v>
+        <v>157.7</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>9500</v>
+        <v>1000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>98040</v>
+        <v>157700</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>D20260914M08</t>
+          <t>D20260914M11</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1523,17 +1523,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>603259</t>
+          <t>300759</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1542,20 +1542,102 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>157.7</v>
+        <v>42.65</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>157700</v>
+        <v>42650</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>D20260914M11</t>
+          <t>D20260916M03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>赤峰黄金</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>600988</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>392040</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>D20260916M02</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>441420</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>D20260916M04</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
@@ -1572,7 +1654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1634,17 +1716,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.523</v>
+        <v>4.55</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1171005</v>
+        <v>1177995</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-30550</v>
+        <v>-23560</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-1.96%</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1743,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.9</v>
+        <v>53.51</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1142680</v>
+        <v>1134412</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-47064</v>
+        <v>-55332</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-4.65%</t>
         </is>
       </c>
     </row>
@@ -1682,23 +1764,23 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>19300</v>
+        <v>12300</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31.68</v>
+        <v>32.17</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>611424</v>
+        <v>395691</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-43358</v>
+        <v>-21605</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-6.62%</t>
+          <t>-5.18%</t>
         </is>
       </c>
     </row>
@@ -1715,17 +1797,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.5</v>
+        <v>28.46</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>265050</v>
+        <v>264678</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5717</v>
+        <v>5345</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+2.20%</t>
+          <t>+2.06%</t>
         </is>
       </c>
     </row>
@@ -1940,6 +2022,60 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>康龙化成</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>42650</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>赤峰黄金</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>392040</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -1982,7 +2118,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-31358</v>
+        <v>-51704</v>
       </c>
     </row>
     <row r="3">
@@ -2092,7 +2228,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>802552.6</v>
+        <v>585002.6</v>
       </c>
     </row>
     <row r="4">
@@ -2102,7 +2238,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4046730.7</v>
+        <v>4264038</v>
       </c>
     </row>
     <row r="5">
@@ -2112,7 +2248,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4849283.3</v>
+        <v>4849040.6</v>
       </c>
     </row>
     <row r="6">
@@ -2123,7 +2259,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.01%</t>
+          <t>-3.02%</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2270,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3184.01</v>
+        <v>3455.54</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1716,17 +1716,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.55</v>
+        <v>4.532</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1177995</v>
+        <v>1173335</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-23560</v>
+        <v>-28220</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
@@ -1743,17 +1743,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.51</v>
+        <v>53.35</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1134412</v>
+        <v>1131020</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-55332</v>
+        <v>-58724</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-4.65%</t>
+          <t>-4.94%</t>
         </is>
       </c>
     </row>
@@ -1770,17 +1770,17 @@
         <v>33.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32.17</v>
+        <v>30.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>395691</v>
+        <v>380070</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-21605</v>
+        <v>-37226</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-5.18%</t>
+          <t>-8.92%</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4264038</v>
+        <v>4240364.8</v>
       </c>
     </row>
     <row r="5">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4849040.6</v>
+        <v>4825367.4</v>
       </c>
     </row>
     <row r="6">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-3.49%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1643,6 +1643,170 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>赤峰黄金</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>600988</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>213700</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M02</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>601318</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>160620</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M01</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>183960</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M03</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>194670</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>D2026091701</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1654,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1737,7 +1901,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21200</v>
+        <v>18200</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>56.12</v>
@@ -1746,10 +1910,10 @@
         <v>53.35</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1131020</v>
+        <v>970970</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-58724</v>
+        <v>-50414</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1760,74 +1924,74 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12300</v>
+        <v>9300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>33.927</v>
+        <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>30.9</v>
+        <v>28.46</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>380070</v>
+        <v>264678</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-37226</v>
+        <v>5345</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-8.92%</t>
+          <t>+2.06%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>27.885</v>
+        <v>10.473</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.46</v>
+        <v>10.47263157894737</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>264678</v>
+        <v>99490</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5345</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+2.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9500</v>
+        <v>5000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10.473</v>
+        <v>17.52</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10.47263157894737</v>
+        <v>17.52</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>99490</v>
+        <v>87600</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -1841,20 +2005,20 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5000</v>
+        <v>6100</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>87600</v>
+        <v>218807</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1868,20 +2032,20 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6100</v>
+        <v>500</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>218807</v>
+        <v>68365</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -1895,20 +2059,20 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68365</v>
+        <v>36650</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -1922,20 +2086,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>36650</v>
+        <v>10380</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -1949,20 +2113,20 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>睿创微纳</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10380</v>
+        <v>177580</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -1976,20 +2140,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>睿创微纳</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>177.58</v>
+        <v>157.7</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>177.58</v>
+        <v>157.7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>177580</v>
+        <v>157700</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2003,20 +2167,20 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>157.7</v>
+        <v>42.65</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>157.7</v>
+        <v>42.65</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>157700</v>
+        <v>42650</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2030,52 +2194,25 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>赤峰黄金</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42650</v>
+        <v>174240</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>赤峰黄金</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>392040</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -2092,7 +2229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2118,7 +2255,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-51704</v>
+        <v>-90370</v>
       </c>
     </row>
     <row r="3">
@@ -2179,6 +2316,26 @@
       </c>
       <c r="B8" s="2" t="n">
         <v>-1450</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>600988</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>-4100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>601318</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-7740</v>
       </c>
     </row>
   </sheetData>
@@ -2228,7 +2385,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>585002.6</v>
+        <v>1337952.6</v>
       </c>
     </row>
     <row r="4">
@@ -2238,7 +2395,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4240364.8</v>
+        <v>3482444.8</v>
       </c>
     </row>
     <row r="5">
@@ -2248,7 +2405,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4825367.4</v>
+        <v>4820397.4</v>
       </c>
     </row>
     <row r="6">
@@ -2259,7 +2416,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-3.59%</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2427,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3455.54</v>
+        <v>4020.25</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1807,6 +1807,47 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>11800</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>370638</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>D2026091801</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1818,7 +1859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1880,17 +1921,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.532</v>
+        <v>4.582</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1173335</v>
+        <v>1186280</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-28220</v>
+        <v>-15275</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-1.27%</t>
         </is>
       </c>
     </row>
@@ -1907,91 +1948,91 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.35</v>
+        <v>53.37</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>970970</v>
+        <v>971334</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-50414</v>
+        <v>-50050</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-4.94%</t>
+          <t>-4.90%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9300</v>
+        <v>11800</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27.885</v>
+        <v>31.41</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>28.46</v>
+        <v>31.41</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>264678</v>
+        <v>370638</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5345</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+2.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9500</v>
+        <v>9300</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10.473</v>
+        <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10.47263157894737</v>
+        <v>28.27</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99490</v>
+        <v>262911</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>3578</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.38%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5000</v>
+        <v>9500</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>17.52</v>
+        <v>10.473</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17.52</v>
+        <v>10.47263157894737</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>87600</v>
+        <v>99490</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2005,20 +2046,20 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6100</v>
+        <v>5000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>35.87</v>
+        <v>17.52</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35.87</v>
+        <v>17.52</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>218807</v>
+        <v>87600</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2032,20 +2073,20 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>500</v>
+        <v>6100</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>136.73</v>
+        <v>35.87</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>136.73</v>
+        <v>35.87</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>68365</v>
+        <v>218807</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2059,20 +2100,20 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7.33</v>
+        <v>136.73</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7.33</v>
+        <v>136.73</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>36650</v>
+        <v>68365</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2086,20 +2127,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>20.76</v>
+        <v>7.33</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20.76</v>
+        <v>7.33</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10380</v>
+        <v>36650</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -2113,20 +2154,20 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>睿创微纳</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>177.58</v>
+        <v>20.76</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>177.58</v>
+        <v>20.76</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>177580</v>
+        <v>10380</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2140,20 +2181,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>睿创微纳</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>157.7</v>
+        <v>177.58</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>157.7</v>
+        <v>177.58</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>157700</v>
+        <v>177580</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2167,20 +2208,20 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>42.65</v>
+        <v>157.7</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>42.65</v>
+        <v>157.7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>42650</v>
+        <v>157700</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2194,25 +2235,52 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>赤峰黄金</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>43.56</v>
+        <v>42.65</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>43.56</v>
+        <v>42.65</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>174240</v>
+        <v>42650</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>赤峰黄金</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>174240</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -2385,7 +2453,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1337952.6</v>
+        <v>967314.6</v>
       </c>
     </row>
     <row r="4">
@@ -2395,7 +2463,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3482444.8</v>
+        <v>3864624.8</v>
       </c>
     </row>
     <row r="5">
@@ -2405,7 +2473,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4820397.4</v>
+        <v>4831939.4</v>
       </c>
     </row>
     <row r="6">
@@ -2416,7 +2484,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.59%</t>
+          <t>-3.36%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2495,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4020.25</v>
+        <v>4112.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1832,10 +1832,10 @@
         <v>31.41</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>11800</v>
+        <v>10300</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>370638</v>
+        <v>323523</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1845,6 +1845,47 @@
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>603259</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>159.35</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>47805</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>D20260918M01</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -1969,7 +2010,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11800</v>
+        <v>10300</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>31.41</v>
@@ -1978,7 +2019,7 @@
         <v>31.41</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>370638</v>
+        <v>323523</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -2212,16 +2253,16 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>157.7</v>
+        <v>158.081</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>157.7</v>
+        <v>158.0807692307692</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>157700</v>
+        <v>205505</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2453,7 +2494,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>967314.6</v>
+        <v>966624.6</v>
       </c>
     </row>
     <row r="4">
@@ -2463,7 +2504,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3864624.8</v>
+        <v>3865314.8</v>
       </c>
     </row>
     <row r="5">
@@ -2495,7 +2536,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4112.91</v>
+        <v>4113.08</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1962,17 +1962,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.582</v>
+        <v>4.608</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1186280</v>
+        <v>1193011</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-15275</v>
+        <v>-8544</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>-0.71%</t>
         </is>
       </c>
     </row>
@@ -1989,17 +1989,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.37</v>
+        <v>53.98</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>971334</v>
+        <v>982436</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-50050</v>
+        <v>-38948</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-4.90%</t>
+          <t>-3.81%</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2016,17 @@
         <v>31.41</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31.41</v>
+        <v>31.3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>323523</v>
+        <v>322390</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>-1133</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.35%</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.27</v>
+        <v>28.1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>262911</v>
+        <v>261330</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3578</v>
+        <v>1997</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+0.77%</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3865314.8</v>
+        <v>3880434.2</v>
       </c>
     </row>
     <row r="5">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4831939.4</v>
+        <v>4847058.8</v>
       </c>
     </row>
     <row r="6">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.36%</t>
+          <t>-3.06%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1962,17 +1962,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.608</v>
+        <v>4.613</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1193011</v>
+        <v>1194306</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-8544</v>
+        <v>-7249</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-0.60%</t>
         </is>
       </c>
     </row>
@@ -1989,17 +1989,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.98</v>
+        <v>54.46</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>982436</v>
+        <v>991172</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-38948</v>
+        <v>-30212</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-3.81%</t>
+          <t>-2.96%</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2016,17 @@
         <v>31.41</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31.3</v>
+        <v>31.41</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>322390</v>
+        <v>323523</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-1133</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.1</v>
+        <v>28.02</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>261330</v>
+        <v>260586</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1997</v>
+        <v>1253</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+0.48%</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3880434.2</v>
+        <v>3890853.7</v>
       </c>
     </row>
     <row r="5">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4847058.8</v>
+        <v>4857478.3</v>
       </c>
     </row>
     <row r="6">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>-2.85%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1962,17 +1962,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.613</v>
+        <v>4.59</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1194306</v>
+        <v>1188351</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-7249</v>
+        <v>-13204</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>-1.10%</t>
         </is>
       </c>
     </row>
@@ -1989,17 +1989,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>54.46</v>
+        <v>53.87</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>991172</v>
+        <v>980434</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-30212</v>
+        <v>-40950</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-2.96%</t>
+          <t>-4.01%</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.02</v>
+        <v>28.08</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>260586</v>
+        <v>261144</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1253</v>
+        <v>1811</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+0.70%</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3890853.7</v>
+        <v>3874719</v>
       </c>
     </row>
     <row r="5">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4857478.3</v>
+        <v>4841343.6</v>
       </c>
     </row>
     <row r="6">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-3.17%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -1962,17 +1962,17 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.59</v>
+        <v>4.515</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1188351</v>
+        <v>1168934</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-13204</v>
+        <v>-32621</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-1.10%</t>
+          <t>-2.71%</t>
         </is>
       </c>
     </row>
@@ -1989,17 +1989,17 @@
         <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.87</v>
+        <v>53.25</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>980434</v>
+        <v>969150</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-40950</v>
+        <v>-52234</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>-5.11%</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2016,17 @@
         <v>31.41</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31.41</v>
+        <v>30.01</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>323523</v>
+        <v>309103</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>-14420</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-4.46%</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
         <v>27.885</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.08</v>
+        <v>28.36</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>261144</v>
+        <v>263748</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1811</v>
+        <v>4415</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>+1.70%</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3874719</v>
+        <v>3832201.5</v>
       </c>
     </row>
     <row r="5">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4841343.6</v>
+        <v>4798826.1</v>
       </c>
     </row>
     <row r="6">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>-4.02%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1889,6 +1889,47 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪深300ETF</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>258900</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>1143561.3</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>D2026092801</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1900,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1952,128 +1993,128 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>258900</v>
+        <v>18200</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.641</v>
+        <v>56.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.515</v>
+        <v>52.4</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1168934</v>
+        <v>953680</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-32621</v>
+        <v>-67704</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-6.63%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>18200</v>
+        <v>10300</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>56.12</v>
+        <v>31.41</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.25</v>
+        <v>29.42</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>969150</v>
+        <v>303026</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-52234</v>
+        <v>-20497</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>-6.34%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10300</v>
+        <v>9300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>31.41</v>
+        <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>30.01</v>
+        <v>28.55</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>309103</v>
+        <v>265515</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-14420</v>
+        <v>6182</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-4.46%</t>
+          <t>+2.38%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>27.885</v>
+        <v>10.473</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>28.36</v>
+        <v>10.47263157894737</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>263748</v>
+        <v>99490</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4415</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>9500</v>
+        <v>5000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10.473</v>
+        <v>17.52</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10.47263157894737</v>
+        <v>17.52</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>99490</v>
+        <v>87600</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2087,20 +2128,20 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5000</v>
+        <v>6100</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>87600</v>
+        <v>218807</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2114,20 +2155,20 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6100</v>
+        <v>500</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>218807</v>
+        <v>68365</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2141,20 +2182,20 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68365</v>
+        <v>36650</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2168,20 +2209,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>36650</v>
+        <v>10380</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -2195,20 +2236,20 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>睿创微纳</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10380</v>
+        <v>177580</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2222,20 +2263,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>睿创微纳</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>177.58</v>
+        <v>158.081</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>177.58</v>
+        <v>158.0807692307692</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>177580</v>
+        <v>205505</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2249,20 +2290,20 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>158.081</v>
+        <v>42.65</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>158.0807692307692</v>
+        <v>42.65</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>205505</v>
+        <v>42650</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2276,52 +2317,25 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>赤峰黄金</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>42650</v>
+        <v>174240</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>赤峰黄金</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>174240</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -2338,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2445,6 +2459,16 @@
       </c>
       <c r="B10" s="2" t="n">
         <v>-7740</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>510300</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>-57994</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +2518,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>966624.6</v>
+        <v>2110185.9</v>
       </c>
     </row>
     <row r="4">
@@ -2504,7 +2528,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3832201.5</v>
+        <v>2643488</v>
       </c>
     </row>
     <row r="5">
@@ -2514,7 +2538,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4798826.1</v>
+        <v>4753673.9</v>
       </c>
     </row>
     <row r="6">
@@ -2525,7 +2549,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-4.93%</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2560,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4113.08</v>
+        <v>4970.75</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1930,6 +1930,88 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>315480</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>D2026092902</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>28300</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>836265</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>D2026092901</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1941,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2003,17 +2085,17 @@
         <v>56.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>953680</v>
+        <v>955500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-67704</v>
+        <v>-65884</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-6.63%</t>
+          <t>-6.45%</t>
         </is>
       </c>
     </row>
@@ -2024,23 +2106,23 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>10300</v>
+        <v>38600</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>31.41</v>
+        <v>30.046</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.42</v>
+        <v>29.46</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>303026</v>
+        <v>1137156</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-20497</v>
+        <v>-22632</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-6.34%</t>
+          <t>-1.95%</t>
         </is>
       </c>
     </row>
@@ -2057,17 +2139,17 @@
         <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>28.55</v>
+        <v>28.38</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>265515</v>
+        <v>263934</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6182</v>
+        <v>4601</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>+1.77%</t>
         </is>
       </c>
     </row>
@@ -2336,6 +2418,33 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>315480</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -2518,7 +2627,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2110185.9</v>
+        <v>958440.9</v>
       </c>
     </row>
     <row r="4">
@@ -2528,7 +2637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2643488</v>
+        <v>3793337</v>
       </c>
     </row>
     <row r="5">
@@ -2538,7 +2647,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4753673.9</v>
+        <v>4751777.9</v>
       </c>
     </row>
     <row r="6">
@@ -2549,7 +2658,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>-4.96%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2669,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4970.75</v>
+        <v>5258.69</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2085,17 +2085,17 @@
         <v>56.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>52.5</v>
+        <v>53.29</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>955500</v>
+        <v>969878</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-65884</v>
+        <v>-51506</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-6.45%</t>
+          <t>-5.04%</t>
         </is>
       </c>
     </row>
@@ -2112,17 +2112,17 @@
         <v>30.046</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.46</v>
+        <v>29.79</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1137156</v>
+        <v>1149894</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-22632</v>
+        <v>-9894</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-0.85%</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2139,17 @@
         <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>28.38</v>
+        <v>28.54</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>263934</v>
+        <v>265422</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4601</v>
+        <v>6089</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+2.35%</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
         <v>286.8</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>286.8</v>
+        <v>291.11</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>315480</v>
+        <v>320221</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>4741</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.50%</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3793337</v>
+        <v>3826682</v>
       </c>
     </row>
     <row r="5">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4751777.9</v>
+        <v>4785122.9</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-4.96%</t>
+          <t>-4.30%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2085,17 +2085,17 @@
         <v>56.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>53.29</v>
+        <v>52.67</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>969878</v>
+        <v>958594</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-51506</v>
+        <v>-62790</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-5.04%</t>
+          <t>-6.15%</t>
         </is>
       </c>
     </row>
@@ -2112,17 +2112,17 @@
         <v>30.046</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.79</v>
+        <v>29.37</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1149894</v>
+        <v>1133682</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-9894</v>
+        <v>-26106</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-2.25%</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2139,17 @@
         <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>28.54</v>
+        <v>28.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>265422</v>
+        <v>268770</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6089</v>
+        <v>9437</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+2.35%</t>
+          <t>+3.64%</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
         <v>286.8</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>291.11</v>
+        <v>286.75</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>320221</v>
+        <v>315425</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>4741</v>
+        <v>-55</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>-0.02%</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3826682</v>
+        <v>3797738</v>
       </c>
     </row>
     <row r="5">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4785122.9</v>
+        <v>4756178.9</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-4.30%</t>
+          <t>-4.88%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2085,17 +2085,17 @@
         <v>56.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>52.67</v>
+        <v>52.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>958594</v>
+        <v>961506</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-62790</v>
+        <v>-59878</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-6.15%</t>
+          <t>-5.86%</t>
         </is>
       </c>
     </row>
@@ -2112,17 +2112,17 @@
         <v>30.046</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.37</v>
+        <v>30.8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1133682</v>
+        <v>1188880</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-26106</v>
+        <v>29092</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+2.51%</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2139,17 @@
         <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>28.9</v>
+        <v>28.99</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>268770</v>
+        <v>269607</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>9437</v>
+        <v>10274</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+3.64%</t>
+          <t>+3.96%</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
         <v>286.8</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>286.75</v>
+        <v>297.75</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>315425</v>
+        <v>327525</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-55</v>
+        <v>12045</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+3.82%</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3797738</v>
+        <v>3868785</v>
       </c>
     </row>
     <row r="5">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4756178.9</v>
+        <v>4827225.9</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-4.88%</t>
+          <t>-3.46%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2085,17 +2085,17 @@
         <v>56.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>52.83</v>
+        <v>53.24</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>961506</v>
+        <v>968968</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-59878</v>
+        <v>-52416</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-5.86%</t>
+          <t>-5.13%</t>
         </is>
       </c>
     </row>
@@ -2112,17 +2112,17 @@
         <v>30.046</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>30.8</v>
+        <v>30.22</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1188880</v>
+        <v>1166492</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29092</v>
+        <v>6704</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>+0.58%</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2139,17 @@
         <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>28.99</v>
+        <v>29.38</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>269607</v>
+        <v>273234</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10274</v>
+        <v>13901</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+3.96%</t>
+          <t>+5.36%</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
         <v>286.8</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>297.75</v>
+        <v>298.38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>327525</v>
+        <v>328218</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>12045</v>
+        <v>12738</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>+3.82%</t>
+          <t>+4.04%</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3868785</v>
+        <v>3858179</v>
       </c>
     </row>
     <row r="5">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4827225.9</v>
+        <v>4816619.9</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-3.67%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2085,17 +2085,17 @@
         <v>56.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>53.24</v>
+        <v>51.69</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>968968</v>
+        <v>940758</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-52416</v>
+        <v>-80626</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-5.13%</t>
+          <t>-7.89%</t>
         </is>
       </c>
     </row>
@@ -2112,17 +2112,17 @@
         <v>30.046</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>30.22</v>
+        <v>30.4</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1166492</v>
+        <v>1173440</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6704</v>
+        <v>13652</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>+1.18%</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2139,17 @@
         <v>27.885</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>29.38</v>
+        <v>29.15</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>273234</v>
+        <v>271095</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13901</v>
+        <v>11762</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+5.36%</t>
+          <t>+4.54%</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
         <v>286.8</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>298.38</v>
+        <v>289.1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>328218</v>
+        <v>318010</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>12738</v>
+        <v>2530</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>+4.04%</t>
+          <t>+0.80%</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3858179</v>
+        <v>3824570</v>
       </c>
     </row>
     <row r="5">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4816619.9</v>
+        <v>4783010.9</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-3.67%</t>
+          <t>-4.34%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2012,6 +2012,47 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>601318</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>932386</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>D2026101401</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2023,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2075,101 +2116,101 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>18200</v>
+        <v>38600</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>56.12</v>
+        <v>30.046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>51.69</v>
+        <v>29.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>940758</v>
+        <v>1157228</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-80626</v>
+        <v>-2560</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-7.89%</t>
+          <t>-0.22%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>38600</v>
+        <v>9300</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>30.046</v>
+        <v>27.885</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>30.4</v>
+        <v>29.45</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1173440</v>
+        <v>273885</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13652</v>
+        <v>14552</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>+5.61%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9300</v>
+        <v>9500</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27.885</v>
+        <v>10.473</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>29.15</v>
+        <v>10.47263157894737</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>271095</v>
+        <v>99490</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11762</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+4.54%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9500</v>
+        <v>5000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10.473</v>
+        <v>17.52</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10.47263157894737</v>
+        <v>17.52</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99490</v>
+        <v>87600</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -2183,20 +2224,20 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5000</v>
+        <v>6100</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>87600</v>
+        <v>218807</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2210,20 +2251,20 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6100</v>
+        <v>500</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>218807</v>
+        <v>68365</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2237,20 +2278,20 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>68365</v>
+        <v>36650</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2264,20 +2305,20 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>36650</v>
+        <v>10380</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2291,20 +2332,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>睿创微纳</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10380</v>
+        <v>177580</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -2318,20 +2359,20 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>睿创微纳</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>177.58</v>
+        <v>158.081</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>177.58</v>
+        <v>158.0807692307692</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>177580</v>
+        <v>205505</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2345,20 +2386,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>158.081</v>
+        <v>42.65</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>158.0807692307692</v>
+        <v>42.65</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>205505</v>
+        <v>42650</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2372,20 +2413,20 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>赤峰黄金</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>42650</v>
+        <v>174240</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -2399,54 +2440,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>赤峰黄金</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4000</v>
+        <v>1100</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>43.56</v>
+        <v>286.8</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>43.56</v>
+        <v>280.12</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>174240</v>
+        <v>308132</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>-7348</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>宁德时代</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>286.8</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>289.1</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>318010</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>2530</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>+0.80%</t>
+          <t>-2.33%</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2581,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-7740</v>
+        <v>-96738</v>
       </c>
     </row>
     <row r="11">
@@ -2627,7 +2641,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>958440.9</v>
+        <v>1890826.9</v>
       </c>
     </row>
     <row r="4">
@@ -2637,7 +2651,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3824570</v>
+        <v>2860512</v>
       </c>
     </row>
     <row r="5">
@@ -2647,7 +2661,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4783010.9</v>
+        <v>4751338.9</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-4.34%</t>
+          <t>-4.97%</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2683,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5258.69</v>
+        <v>5957.98</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2048,47 @@
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>600900</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>858400</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>D2026101501</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
@@ -2126,17 +2167,17 @@
         <v>30.046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.98</v>
+        <v>29.38</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1157228</v>
+        <v>1134068</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2560</v>
+        <v>-25720</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-2.22%</t>
         </is>
       </c>
     </row>
@@ -2147,23 +2188,23 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9300</v>
+        <v>38300</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>27.885</v>
+        <v>29.184</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.45</v>
+        <v>29.6</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>273885</v>
+        <v>1133680</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14552</v>
+        <v>15947</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+5.61%</t>
+          <t>+1.43%</t>
         </is>
       </c>
     </row>
@@ -2450,17 +2491,17 @@
         <v>286.8</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>280.12</v>
+        <v>278.5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>308132</v>
+        <v>306350</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-7348</v>
+        <v>-9130</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-2.89%</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2682,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1890826.9</v>
+        <v>1032426.9</v>
       </c>
     </row>
     <row r="4">
@@ -2651,7 +2692,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2860512</v>
+        <v>3695365</v>
       </c>
     </row>
     <row r="5">
@@ -2661,7 +2702,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4751338.9</v>
+        <v>4727791.9</v>
       </c>
     </row>
     <row r="6">
@@ -2672,7 +2713,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-4.97%</t>
+          <t>-5.44%</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2724,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5957.98</v>
+        <v>6172.58</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2167,17 +2167,17 @@
         <v>30.046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.38</v>
+        <v>29.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1134068</v>
+        <v>1154912</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-25720</v>
+        <v>-4876</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-0.42%</t>
         </is>
       </c>
     </row>
@@ -2194,17 +2194,17 @@
         <v>29.184</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.6</v>
+        <v>29.38</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1133680</v>
+        <v>1125254</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15947</v>
+        <v>7521</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+0.67%</t>
         </is>
       </c>
     </row>
@@ -2491,17 +2491,17 @@
         <v>286.8</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>278.5</v>
+        <v>277</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>306350</v>
+        <v>304700</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-9130</v>
+        <v>-10780</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-3.42%</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3695365</v>
+        <v>3706133</v>
       </c>
     </row>
     <row r="5">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4727791.9</v>
+        <v>4738559.9</v>
       </c>
     </row>
     <row r="6">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-5.44%</t>
+          <t>-5.23%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2094,6 +2094,47 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>267.02</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>293722</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>D2026101901</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2105,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2167,17 +2208,17 @@
         <v>30.046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.92</v>
+        <v>29.79</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1154912</v>
+        <v>1149894</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4876</v>
+        <v>-9894</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.85%</t>
         </is>
       </c>
     </row>
@@ -2194,17 +2235,17 @@
         <v>29.184</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.38</v>
+        <v>29.54</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1125254</v>
+        <v>1131382</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>7521</v>
+        <v>13649</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+1.22%</t>
         </is>
       </c>
     </row>
@@ -2475,33 +2516,6 @@
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>宁德时代</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>286.8</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>277</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>304700</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-10780</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3.42%</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2633,6 +2647,16 @@
       </c>
       <c r="B11" s="2" t="n">
         <v>-57994</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>-21758</v>
       </c>
     </row>
   </sheetData>
@@ -2682,7 +2706,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1032426.9</v>
+        <v>1326148.9</v>
       </c>
     </row>
     <row r="4">
@@ -2692,7 +2716,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3706133</v>
+        <v>3402543</v>
       </c>
     </row>
     <row r="5">
@@ -2702,7 +2726,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4738559.9</v>
+        <v>4728691.9</v>
       </c>
     </row>
     <row r="6">
@@ -2713,7 +2737,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-5.43%</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2748,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6172.58</v>
+        <v>6392.87</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2135,6 +2135,47 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>美的集团</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>000333</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>383760</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>D2026102001</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2146,7 +2187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2208,17 +2249,17 @@
         <v>30.046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.79</v>
+        <v>29.06</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1149894</v>
+        <v>1121716</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-9894</v>
+        <v>-38072</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-3.28%</t>
         </is>
       </c>
     </row>
@@ -2235,37 +2276,37 @@
         <v>29.184</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.54</v>
+        <v>29.69</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1131382</v>
+        <v>1137127</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13649</v>
+        <v>19394</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+1.74%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9500</v>
+        <v>4500</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10.473</v>
+        <v>85.28</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10.47263157894737</v>
+        <v>85.28</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>99490</v>
+        <v>383760</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -2279,20 +2320,20 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5000</v>
+        <v>9500</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>17.52</v>
+        <v>10.473</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>17.52</v>
+        <v>10.47263157894737</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>87600</v>
+        <v>99490</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -2306,20 +2347,20 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6100</v>
+        <v>5000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>35.87</v>
+        <v>17.52</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>35.87</v>
+        <v>17.52</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>218807</v>
+        <v>87600</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2333,20 +2374,20 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>500</v>
+        <v>6100</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>136.73</v>
+        <v>35.87</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>136.73</v>
+        <v>35.87</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>68365</v>
+        <v>218807</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2360,20 +2401,20 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7.33</v>
+        <v>136.73</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7.33</v>
+        <v>136.73</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>36650</v>
+        <v>68365</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2387,20 +2428,20 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>20.76</v>
+        <v>7.33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>20.76</v>
+        <v>7.33</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10380</v>
+        <v>36650</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2414,20 +2455,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>睿创微纳</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>177.58</v>
+        <v>20.76</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>177.58</v>
+        <v>20.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>177580</v>
+        <v>10380</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -2441,20 +2482,20 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>睿创微纳</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>158.081</v>
+        <v>177.58</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>158.0807692307692</v>
+        <v>177.58</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>205505</v>
+        <v>177580</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2468,20 +2509,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>42.65</v>
+        <v>158.081</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>42.65</v>
+        <v>158.0807692307692</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>42650</v>
+        <v>205505</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2495,25 +2536,52 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>赤峰黄金</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>43.56</v>
+        <v>42.65</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>43.56</v>
+        <v>42.65</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>174240</v>
+        <v>42650</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>赤峰黄金</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>174240</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -2706,7 +2774,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1326148.9</v>
+        <v>942388.9</v>
       </c>
     </row>
     <row r="4">
@@ -2716,7 +2784,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3402543</v>
+        <v>3763870</v>
       </c>
     </row>
     <row r="5">
@@ -2726,7 +2794,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4728691.9</v>
+        <v>4706258.9</v>
       </c>
     </row>
     <row r="6">
@@ -2737,7 +2805,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-5.43%</t>
+          <t>-5.87%</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2816,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6392.87</v>
+        <v>6488.81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2249,17 +2249,17 @@
         <v>30.046</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.06</v>
+        <v>28.87</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1121716</v>
+        <v>1114382</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-38072</v>
+        <v>-45406</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-3.92%</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
         <v>29.184</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.69</v>
+        <v>29.57</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1137127</v>
+        <v>1132531</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>19394</v>
+        <v>14798</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>+1.32%</t>
         </is>
       </c>
     </row>
@@ -2303,17 +2303,17 @@
         <v>85.28</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>85.28</v>
+        <v>83.86</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>383760</v>
+        <v>377370</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>-6390</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-1.67%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3763870</v>
+        <v>3745550</v>
       </c>
     </row>
     <row r="5">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4706258.9</v>
+        <v>4687938.9</v>
       </c>
     </row>
     <row r="6">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-5.87%</t>
+          <t>-6.24%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2176,47 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>38600</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1074624</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>D2026102201</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2187,7 +2228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2239,101 +2280,101 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>38600</v>
+        <v>38300</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>30.046</v>
+        <v>29.184</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28.87</v>
+        <v>29.82</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1114382</v>
+        <v>1142106</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-45406</v>
+        <v>24373</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-3.92%</t>
+          <t>+2.18%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>38300</v>
+        <v>4500</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>29.184</v>
+        <v>85.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29.57</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1132531</v>
+        <v>383805</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14798</v>
+        <v>45</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>+0.01%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>新集能源</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4500</v>
+        <v>9500</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>85.28</v>
+        <v>10.473</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>83.86</v>
+        <v>10.47263157894737</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>377370</v>
+        <v>99490</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6390</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>新集能源</t>
+          <t>恺英网络</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9500</v>
+        <v>5000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10.473</v>
+        <v>17.52</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10.47263157894737</v>
+        <v>17.52</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99490</v>
+        <v>87600</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -2347,20 +2388,20 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>星网锐捷</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5000</v>
+        <v>6100</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17.52</v>
+        <v>35.87</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>87600</v>
+        <v>218807</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2374,20 +2415,20 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>星网锐捷</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6100</v>
+        <v>500</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>35.87</v>
+        <v>136.73</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>218807</v>
+        <v>68365</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2401,20 +2442,20 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>哈药股份</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>136.73</v>
+        <v>7.33</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>68365</v>
+        <v>36650</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2428,20 +2469,20 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>哈药股份</t>
+          <t>招商轮船</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7.33</v>
+        <v>20.76</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>36650</v>
+        <v>10380</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -2455,20 +2496,20 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>睿创微纳</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>20.76</v>
+        <v>177.58</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10380</v>
+        <v>177580</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -2482,20 +2523,20 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>睿创微纳</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>177.58</v>
+        <v>158.081</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>177.58</v>
+        <v>158.0807692307692</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>177580</v>
+        <v>205505</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2509,20 +2550,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>158.081</v>
+        <v>42.65</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>158.0807692307692</v>
+        <v>42.65</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>205505</v>
+        <v>42650</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -2536,52 +2577,25 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>康龙化成</t>
+          <t>赤峰黄金</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>42.65</v>
+        <v>43.56</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>42650</v>
+        <v>174240</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>赤峰黄金</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>174240</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -2624,7 +2638,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-90370</v>
+        <v>-175534</v>
       </c>
     </row>
     <row r="3">
@@ -2774,7 +2788,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>942388.9</v>
+        <v>2017012.9</v>
       </c>
     </row>
     <row r="4">
@@ -2784,7 +2798,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3745550</v>
+        <v>2647178</v>
       </c>
     </row>
     <row r="5">
@@ -2794,7 +2808,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4687938.9</v>
+        <v>4664190.9</v>
       </c>
     </row>
     <row r="6">
@@ -2805,7 +2819,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-6.24%</t>
+          <t>-6.72%</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2830,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6488.81</v>
+        <v>7294.78</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2217,6 +2217,47 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1069200</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>D2026102301</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2228,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2290,17 +2331,17 @@
         <v>29.184</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.82</v>
+        <v>29.45</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1142106</v>
+        <v>1127935</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>24373</v>
+        <v>10202</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>+0.91%</t>
         </is>
       </c>
     </row>
@@ -2317,17 +2358,17 @@
         <v>85.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>85.29000000000001</v>
+        <v>85.59</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>383805</v>
+        <v>385155</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45</v>
+        <v>1395</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.36%</t>
         </is>
       </c>
     </row>
@@ -2596,6 +2637,33 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1069200</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
@@ -2788,7 +2856,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2017012.9</v>
+        <v>947812.9</v>
       </c>
     </row>
     <row r="4">
@@ -2798,7 +2866,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2647178</v>
+        <v>3703557</v>
       </c>
     </row>
     <row r="5">
@@ -2808,7 +2876,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4664190.9</v>
+        <v>4651369.9</v>
       </c>
     </row>
     <row r="6">
@@ -2819,7 +2887,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-6.72%</t>
+          <t>-6.97%</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2898,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7294.78</v>
+        <v>7562.08</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2331,17 +2331,17 @@
         <v>29.184</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.45</v>
+        <v>29.86</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1127935</v>
+        <v>1143638</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10202</v>
+        <v>25905</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+0.91%</t>
+          <t>+2.32%</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
         <v>85.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>85.59</v>
+        <v>85.5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>385155</v>
+        <v>384750</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1395</v>
+        <v>990</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.26%</t>
         </is>
       </c>
     </row>
@@ -2655,17 +2655,17 @@
         <v>237.6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>237.6</v>
+        <v>238</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1069200</v>
+        <v>1071000</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.17%</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3703557</v>
+        <v>3720655</v>
       </c>
     </row>
     <row r="5">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4651369.9</v>
+        <v>4668467.9</v>
       </c>
     </row>
     <row r="6">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-6.97%</t>
+          <t>-6.63%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2331,17 +2331,17 @@
         <v>29.184</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.86</v>
+        <v>29.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1143638</v>
+        <v>1142489</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>25905</v>
+        <v>24756</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+2.32%</t>
+          <t>+2.21%</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
         <v>85.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>85.5</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>384750</v>
+        <v>382680</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>990</v>
+        <v>-1080</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.28%</t>
         </is>
       </c>
     </row>
@@ -2655,17 +2655,17 @@
         <v>237.6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1071000</v>
+        <v>1048500</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1800</v>
+        <v>-20700</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-1.94%</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3720655</v>
+        <v>3694936</v>
       </c>
     </row>
     <row r="5">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4668467.9</v>
+        <v>4642748.9</v>
       </c>
     </row>
     <row r="6">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-6.63%</t>
+          <t>-7.15%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2331,17 +2331,17 @@
         <v>29.184</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.83</v>
+        <v>29.4</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1142489</v>
+        <v>1126020</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>24756</v>
+        <v>8287</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+2.21%</t>
+          <t>+0.74%</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
         <v>85.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>85.04000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>382680</v>
+        <v>386595</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-1080</v>
+        <v>2835</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.74%</t>
         </is>
       </c>
     </row>
@@ -2655,17 +2655,17 @@
         <v>237.6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>233</v>
+        <v>229.14</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1048500</v>
+        <v>1031130</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-20700</v>
+        <v>-38070</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-3.56%</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3694936</v>
+        <v>3665012</v>
       </c>
     </row>
     <row r="5">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4642748.9</v>
+        <v>4612824.9</v>
       </c>
     </row>
     <row r="6">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-7.15%</t>
+          <t>-7.74%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2331,17 +2331,17 @@
         <v>29.184</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.4</v>
+        <v>29.99</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1126020</v>
+        <v>1148617</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>8287</v>
+        <v>30884</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.76%</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
         <v>85.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>85.91</v>
+        <v>87.48</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>386595</v>
+        <v>393660</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2835</v>
+        <v>9900</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+2.58%</t>
         </is>
       </c>
     </row>
@@ -2655,17 +2655,17 @@
         <v>237.6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>229.14</v>
+        <v>229.07</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1031130</v>
+        <v>1030815</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-38070</v>
+        <v>-38385</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-3.59%</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3665012</v>
+        <v>3694359</v>
       </c>
     </row>
     <row r="5">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4612824.9</v>
+        <v>4642171.9</v>
       </c>
     </row>
     <row r="6">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-7.74%</t>
+          <t>-7.16%</t>
         </is>
       </c>
     </row>

--- a/outputs/09_交易日志与盈亏归因.xlsx
+++ b/outputs/09_交易日志与盈亏归因.xlsx
@@ -2331,17 +2331,17 @@
         <v>29.184</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>29.99</v>
+        <v>29.74</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1148617</v>
+        <v>1139042</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30884</v>
+        <v>21309</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+2.76%</t>
+          <t>+1.91%</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
         <v>85.28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>87.48</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>393660</v>
+        <v>401310</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9900</v>
+        <v>17550</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+4.57%</t>
         </is>
       </c>
     </row>
@@ -2655,17 +2655,17 @@
         <v>237.6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>229.07</v>
+        <v>232.92</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1030815</v>
+        <v>1048140</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-38385</v>
+        <v>-21060</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-3.59%</t>
+          <t>-1.97%</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3694359</v>
+        <v>3709759</v>
       </c>
     </row>
     <row r="5">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4642171.9</v>
+        <v>4657571.9</v>
       </c>
     </row>
     <row r="6">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-7.16%</t>
+          <t>-6.85%</t>
         </is>
       </c>
     </row>
